--- a/Programación-2026-1-MCM.xlsx
+++ b/Programación-2026-1-MCM.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -70,13 +70,13 @@
     <t xml:space="preserve">Marzo M3</t>
   </si>
   <si>
-    <t xml:space="preserve">Aplicación: océanos planetarios. Potencial de presión.</t>
+    <t xml:space="preserve">Aplicación: océanos planetarios. Potencial de presión. Aplicación: atmósferas planetarias plano paralelas. </t>
   </si>
   <si>
     <t xml:space="preserve">J5</t>
   </si>
   <si>
-    <t xml:space="preserve">Aplicación: atmósferas planetarias plano paralelas. </t>
+    <t xml:space="preserve">Medios continuos autogravitantes. Ecuaciones del interior de un cuerpo esférico autogravitante. Aplicación: interior de planetas de capas homogéneas.</t>
   </si>
   <si>
     <t xml:space="preserve">V6</t>
@@ -88,13 +88,13 @@
     <t xml:space="preserve">M10</t>
   </si>
   <si>
-    <t xml:space="preserve">Medios continuos autogravitantes. Ecuaciones del interior de un cuerpo esférico autogravitante. </t>
+    <t xml:space="preserve"> Medios continuos politrópicos. Ecuación de Lane-Emden. Aplicación: modelo politrópico del interior estelar. </t>
   </si>
   <si>
     <t xml:space="preserve">J12</t>
   </si>
   <si>
-    <t xml:space="preserve">Aplicación: interior de planetas de capas homogéneas. Medios continuos politrópicos. </t>
+    <t xml:space="preserve">Fronteras de medios. Interfaces de fluidos en equilibrio hidrostático. Fluidos en contenedores acelerados. </t>
   </si>
   <si>
     <t xml:space="preserve">V13</t>
@@ -106,13 +106,13 @@
     <t xml:space="preserve">M17</t>
   </si>
   <si>
-    <t xml:space="preserve">Ecuación de Lane-Emden. Aplicación: modelo politrópico del interior estelar. Fronteras de medios.</t>
+    <t xml:space="preserve">Principio de Arquímedes y estabilidad de cuerpos flotantes. </t>
   </si>
   <si>
     <t xml:space="preserve">J19</t>
   </si>
   <si>
-    <t xml:space="preserve">Principio de Arquímedes y estabilidad de cuerpos flotantes. Tensión superficial. Efecto capilar.</t>
+    <t xml:space="preserve">Tensión superficial. Efecto capilar.</t>
   </si>
   <si>
     <t xml:space="preserve">Primer parcial</t>
@@ -350,7 +350,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -384,6 +384,11 @@
       <name val="Arial"/>
       <family val="1"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -478,7 +483,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -520,6 +525,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="justify" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -527,7 +540,39 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -535,39 +580,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="justify" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -643,112 +656,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
-  <a:themeElements>
-    <a:clrScheme name="LibreOffice">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="ffffff"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="000000"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="ffffff"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="18a303"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="0369a3"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="a33e03"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8e03a3"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="c99c00"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="c9211e"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000ee"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="551a8b"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme>
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -844,7 +751,7 @@
       <c r="XFC10" s="9"/>
       <c r="XFD10" s="9"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -860,7 +767,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
@@ -872,7 +779,7 @@
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="10" t="s">
         <v>24</v>
       </c>
     </row>
@@ -888,10 +795,10 @@
       <c r="A16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="10"/>
+      <c r="E16" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
@@ -914,26 +821,26 @@
       <c r="XFD18" s="9"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="13"/>
+      <c r="D19" s="15"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
       <c r="B20" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="13"/>
+      <c r="C20" s="15"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="17" t="s">
         <v>33</v>
       </c>
     </row>
@@ -958,18 +865,18 @@
       <c r="XFD23" s="9"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="19" t="s">
         <v>37</v>
       </c>
       <c r="XFC25" s="9"/>
@@ -979,7 +886,7 @@
       <c r="A26" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1000,7 +907,7 @@
       <c r="B28" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="19"/>
+      <c r="C28" s="21"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
@@ -1009,7 +916,7 @@
       <c r="B29" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="19"/>
+      <c r="C29" s="21"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
@@ -1031,7 +938,7 @@
       <c r="A32" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B32" s="22" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1042,7 +949,7 @@
       <c r="B33" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C33" s="21"/>
+      <c r="C33" s="23"/>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
@@ -1061,10 +968,10 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="11" t="s">
+      <c r="A36" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="14" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1075,7 +982,7 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="14" t="s">
+      <c r="A38" s="16" t="s">
         <v>59</v>
       </c>
       <c r="B38" s="8" t="s">
@@ -1109,7 +1016,7 @@
       <c r="B41" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C41" s="19"/>
+      <c r="C41" s="21"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
@@ -1139,7 +1046,7 @@
       <c r="A45" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B45" s="22" t="s">
+      <c r="B45" s="24" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1155,7 +1062,7 @@
       <c r="A47" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B47" s="22" t="s">
+      <c r="B47" s="24" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1184,10 +1091,10 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="B51" s="12" t="s">
+      <c r="B51" s="14" t="s">
         <v>84</v>
       </c>
     </row>
@@ -1195,18 +1102,18 @@
       <c r="A52" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B52" s="20" t="s">
+      <c r="B52" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="D52" s="13"/>
+      <c r="D52" s="15"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Página &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Página &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/Programación-2026-1-MCM.xlsx
+++ b/Programación-2026-1-MCM.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="90">
   <si>
     <t xml:space="preserve">Programación Mecánica de Medios Continuos</t>
   </si>
@@ -124,121 +124,142 @@
     <t xml:space="preserve">Cálculo vectorial usando notación de índices. El tensor de esfuerzos.</t>
   </si>
   <si>
+    <t xml:space="preserve">M31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receso Semana Santa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abril J2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M7</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fuerzas en un medio continuo. </t>
   </si>
   <si>
+    <t xml:space="preserve">J9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V10</t>
+  </si>
+  <si>
     <t xml:space="preserve">Quiz 4 y taller</t>
   </si>
   <si>
-    <t xml:space="preserve">M31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Receso Semana Santa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abril J2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M7</t>
+    <t xml:space="preserve">M14</t>
   </si>
   <si>
     <t xml:space="preserve">Del tensor de esfuerzos a la presión</t>
   </si>
   <si>
-    <t xml:space="preserve">J9</t>
+    <t xml:space="preserve">J16</t>
   </si>
   <si>
     <t xml:space="preserve">Regímenes de deformación. </t>
   </si>
   <si>
-    <t xml:space="preserve">V10</t>
+    <t xml:space="preserve">V17</t>
   </si>
   <si>
     <t xml:space="preserve">Quiz 5 y taller</t>
   </si>
   <si>
-    <t xml:space="preserve">M14</t>
+    <t xml:space="preserve">M21</t>
   </si>
   <si>
     <t xml:space="preserve">Del campo de desplazamientos al tensor de deformación. </t>
   </si>
   <si>
-    <t xml:space="preserve">J16</t>
+    <t xml:space="preserve">J23</t>
   </si>
   <si>
     <t xml:space="preserve">Módulos de elasticidad. </t>
   </si>
   <si>
-    <t xml:space="preserve">V17</t>
+    <t xml:space="preserve">V24</t>
   </si>
   <si>
     <t xml:space="preserve">Quiz 6 y taller</t>
   </si>
   <si>
-    <t xml:space="preserve">M21</t>
+    <t xml:space="preserve">M28</t>
   </si>
   <si>
     <t xml:space="preserve">Ecuaciones de la elastostática</t>
   </si>
   <si>
-    <t xml:space="preserve">J23</t>
+    <t xml:space="preserve">J30</t>
   </si>
   <si>
     <t xml:space="preserve">Aplicación: sismología y el interior planetario. </t>
   </si>
   <si>
-    <t xml:space="preserve">V24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M28</t>
+    <t xml:space="preserve">Mayo V1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Día festivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unidad 4: Fluidos en Movimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M5</t>
   </si>
   <si>
     <t xml:space="preserve">Segundo parcial</t>
   </si>
   <si>
-    <t xml:space="preserve">Unidad 4: Fluidos en Movimiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J30</t>
+    <t xml:space="preserve">J7</t>
   </si>
   <si>
     <t xml:space="preserve">Campos en fluídos en movimiento. Flujo incompresible y la ley de Leonardo.</t>
   </si>
   <si>
+    <t xml:space="preserve">V8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quiz 7 y taller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M12</t>
+  </si>
+  <si>
     <t xml:space="preserve">Conservación de la masa y la ecuación de continuidad. El campo de velocidades y su representación.</t>
   </si>
   <si>
-    <t xml:space="preserve">Mayo V1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Día festivo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M5</t>
+    <t xml:space="preserve">J14</t>
   </si>
   <si>
     <t xml:space="preserve">La especificación Euleriana y Lagrangiana. La derivada material y la segunda ley de Newton en fluídos.</t>
   </si>
   <si>
-    <t xml:space="preserve">J7</t>
+    <t xml:space="preserve">V15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quiz 8 y taller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M19</t>
   </si>
   <si>
     <t xml:space="preserve">Aplicación: Cosmología newtoniana. Flujo no viscoso y las ecuaciones de Euler.</t>
   </si>
   <si>
-    <t xml:space="preserve">V8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quiz 7 y taller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M12</t>
+    <t xml:space="preserve">J21</t>
   </si>
   <si>
     <t xml:space="preserve"> El teorema de Bernoulli. El efecto Venturi. </t>
   </si>
   <si>
-    <t xml:space="preserve">J14</t>
+    <t xml:space="preserve">V22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quiz 9 y taller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M26</t>
   </si>
   <si>
     <r>
@@ -261,13 +282,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">V15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quiz 8 y taller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M19</t>
+    <t xml:space="preserve">J28</t>
   </si>
   <si>
     <r>
@@ -290,16 +305,16 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">J21</t>
+    <t xml:space="preserve">V29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2</t>
   </si>
   <si>
     <t xml:space="preserve">Viscosidad newtoniana. El tensor de viscosidad para fluidos newtonianos.</t>
   </si>
   <si>
-    <t xml:space="preserve">V22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M26</t>
+    <t xml:space="preserve">J4</t>
   </si>
   <si>
     <r>
@@ -331,16 +346,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">J28</t>
+    <t xml:space="preserve">V5</t>
   </si>
   <si>
     <t xml:space="preserve">Tercer parcial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quiz computacional</t>
   </si>
 </sst>
 </file>
@@ -350,7 +359,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -386,11 +395,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="11"/>
       <name val="Arial"/>
@@ -411,7 +415,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -427,19 +431,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFB2B2B2"/>
-        <bgColor rgb="FF999999"/>
+        <bgColor rgb="FF969696"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFACB20C"/>
         <bgColor rgb="FF808000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF999999"/>
-        <bgColor rgb="FFB2B2B2"/>
       </patternFill>
     </fill>
     <fill>
@@ -483,7 +481,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -525,14 +523,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="justify" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -540,11 +530,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -552,19 +542,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -576,11 +558,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="justify" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -642,7 +624,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF5983B0"/>
-      <rgbColor rgb="FF999999"/>
+      <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -661,7 +643,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD52"/>
+  <dimension ref="A1:XFD56"/>
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.76"/>
@@ -779,7 +761,7 @@
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="4" t="s">
         <v>24</v>
       </c>
     </row>
@@ -795,10 +777,10 @@
       <c r="A16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="12"/>
+      <c r="E16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
@@ -821,291 +803,320 @@
       <c r="XFD18" s="9"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="15"/>
+      <c r="D19" s="13"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
       <c r="B20" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="15"/>
+      <c r="C20" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>34</v>
+      <c r="A22" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>6</v>
       </c>
       <c r="XFC22" s="9"/>
       <c r="XFD22" s="9"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" s="6" t="s">
+      <c r="A23" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="15" t="s">
         <v>35</v>
       </c>
       <c r="XFC23" s="9"/>
       <c r="XFD23" s="9"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18" t="s">
+      <c r="B25" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>37</v>
       </c>
       <c r="XFC25" s="9"/>
       <c r="XFD25" s="9"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="20" t="s">
-        <v>34</v>
-      </c>
+      <c r="B26" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="XFC26" s="9"/>
+      <c r="XFD26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="2" t="s">
+      <c r="A27" s="5" t="s">
         <v>40</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>41</v>
       </c>
       <c r="XFC27" s="9"/>
       <c r="XFD27" s="9"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B28" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="21"/>
+      <c r="B28" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="XFC28" s="9"/>
+      <c r="XFD28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="6" t="s">
+      <c r="A29" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="21"/>
+      <c r="B29" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="17"/>
+      <c r="XFC29" s="9"/>
+      <c r="XFD29" s="9"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B30" s="2" t="s">
+      <c r="A30" s="5" t="s">
         <v>46</v>
       </c>
+      <c r="B30" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" s="17"/>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>48</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="XFC31" s="9"/>
+      <c r="XFD31" s="9"/>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B32" s="22" t="s">
+      <c r="A32" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="B32" s="2" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B33" s="2" t="s">
+      <c r="A33" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C33" s="23"/>
+      <c r="B33" s="18" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>54</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="C34" s="19"/>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>6</v>
+      <c r="A35" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>57</v>
+      <c r="A36" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2"/>
-      <c r="B37" s="3" t="s">
-        <v>58</v>
-      </c>
+      <c r="A37" s="9"/>
+      <c r="B37" s="9"/>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="B38" s="8" t="s">
+      <c r="A38" s="2"/>
+      <c r="B38" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B39" s="4" t="s">
+      <c r="A39" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="XFC39" s="9"/>
-      <c r="XFD39" s="9"/>
+      <c r="B39" s="12" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B40" s="6" t="s">
+      <c r="A40" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="XFC40" s="9"/>
-      <c r="XFD40" s="9"/>
+      <c r="B40" s="4" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B41" s="4" t="s">
+      <c r="A41" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C41" s="21"/>
+      <c r="B41" s="6" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B43" s="6" t="s">
+      <c r="A43" s="1" t="s">
         <v>69</v>
       </c>
+      <c r="B43" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C43" s="17"/>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B44" s="4" t="s">
+      <c r="A44" s="5" t="s">
         <v>71</v>
       </c>
+      <c r="B44" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C44" s="17"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B45" s="24" t="s">
         <v>73</v>
       </c>
+      <c r="B45" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="XFC45" s="9"/>
+      <c r="XFD45" s="9"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B46" s="6" t="s">
+      <c r="A46" s="1" t="s">
         <v>75</v>
       </c>
+      <c r="B46" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="XFC46" s="9"/>
+      <c r="XFD46" s="9"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B47" s="24" t="s">
+      <c r="A47" s="5" t="s">
         <v>77</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B48" s="4" t="s">
         <v>79</v>
       </c>
+      <c r="B48" s="20" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B49" s="6" t="s">
+      <c r="A49" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B49" s="20" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B50" s="18" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B51" s="14" t="s">
+      <c r="A51" s="1" t="s">
         <v>84</v>
       </c>
+      <c r="B51" s="4" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B52" s="22" t="s">
+      <c r="A52" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D52" s="15"/>
+      <c r="B52" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B53" s="18" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="9"/>
+      <c r="B55" s="9"/>
+    </row>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="9"/>
+      <c r="B56" s="9"/>
+      <c r="D56" s="13"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Programación-2026-1-MCM.xlsx
+++ b/Programación-2026-1-MCM.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="94">
   <si>
     <t xml:space="preserve">Programación Mecánica de Medios Continuos</t>
   </si>
@@ -136,12 +136,15 @@
     <t xml:space="preserve">M7</t>
   </si>
   <si>
-    <t xml:space="preserve">Fuerzas en un medio continuo. </t>
+    <t xml:space="preserve">Fuerzas en un medio continuo. Del tensor de esfuerzos a la presión</t>
   </si>
   <si>
     <t xml:space="preserve">J9</t>
   </si>
   <si>
+    <t xml:space="preserve"> Del campo de desplazamientos al tensor de deformación. </t>
+  </si>
+  <si>
     <t xml:space="preserve">V10</t>
   </si>
   <si>
@@ -151,13 +154,13 @@
     <t xml:space="preserve">M14</t>
   </si>
   <si>
-    <t xml:space="preserve">Del tensor de esfuerzos a la presión</t>
+    <t xml:space="preserve">Significado geométrico del tensor de deformación. Termodinámica de la deformación. Regímenes de deformación.</t>
   </si>
   <si>
     <t xml:space="preserve">J16</t>
   </si>
   <si>
-    <t xml:space="preserve">Regímenes de deformación. </t>
+    <t xml:space="preserve">Cuerpos isótropos: energía libre y módulos de elasticidad. Descomposición del tensor de deformación. Relación tensión-deformación. Ley de Hooke.</t>
   </si>
   <si>
     <t xml:space="preserve">V17</t>
@@ -169,13 +172,13 @@
     <t xml:space="preserve">M21</t>
   </si>
   <si>
-    <t xml:space="preserve">Del campo de desplazamientos al tensor de deformación. </t>
+    <t xml:space="preserve">Deformaciones homogéneas. </t>
   </si>
   <si>
     <t xml:space="preserve">J23</t>
   </si>
   <si>
-    <t xml:space="preserve">Módulos de elasticidad. </t>
+    <t xml:space="preserve">Ecuaciones de la elastostática</t>
   </si>
   <si>
     <t xml:space="preserve">V24</t>
@@ -187,15 +190,12 @@
     <t xml:space="preserve">M28</t>
   </si>
   <si>
-    <t xml:space="preserve">Ecuaciones de la elastostática</t>
+    <t xml:space="preserve">Aplicaciones</t>
   </si>
   <si>
     <t xml:space="preserve">J30</t>
   </si>
   <si>
-    <t xml:space="preserve">Aplicación: sismología y el interior planetario. </t>
-  </si>
-  <si>
     <t xml:space="preserve">Mayo V1</t>
   </si>
   <si>
@@ -214,75 +214,31 @@
     <t xml:space="preserve">J7</t>
   </si>
   <si>
-    <t xml:space="preserve">Campos en fluídos en movimiento. Flujo incompresible y la ley de Leonardo.</t>
+    <t xml:space="preserve">Campos en fluídos en movimiento. Flujo incompresible y la ley de Leonardo. Conservación de la masa y la ecuación de continuidad. El campo de velocidades y su representación.</t>
   </si>
   <si>
     <t xml:space="preserve">V8</t>
   </si>
   <si>
+    <t xml:space="preserve">M12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La especificación Euleriana y Lagrangiana. La derivada material y la segunda ley de Newton en fluídos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aplicación: Cosmología newtoniana. Flujo no viscoso y las ecuaciones de Euler.  El teorema de Bernoulli. El efecto Venturi. La ley de Torricelli. Del campo de Bernoulli a la vorticidad. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">V15</t>
+  </si>
+  <si>
     <t xml:space="preserve">Quiz 7 y taller</t>
   </si>
   <si>
-    <t xml:space="preserve">M12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conservación de la masa y la ecuación de continuidad. El campo de velocidades y su representación.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La especificación Euleriana y Lagrangiana. La derivada material y la segunda ley de Newton en fluídos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quiz 8 y taller</t>
-  </si>
-  <si>
     <t xml:space="preserve">M19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aplicación: Cosmología newtoniana. Flujo no viscoso y las ecuaciones de Euler.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J21</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> El teorema de Bernoulli. El efecto Venturi. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">V22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quiz 9 y taller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M26</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">La ley de Torricelli. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Del campo de Bernoulli a la vorticidad. </t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">J28</t>
   </si>
   <si>
     <r>
@@ -305,27 +261,54 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">J21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ondas en un fluido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quiz 8 y taller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flujo compresible. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">J28</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Viscosidad newtoniana. El tensor de viscosidad para fluidos newtonianos.</t>
+  </si>
+  <si>
     <t xml:space="preserve">V29</t>
   </si>
   <si>
+    <t xml:space="preserve">Quiz 9 y taller</t>
+  </si>
+  <si>
     <t xml:space="preserve">M2</t>
   </si>
   <si>
-    <t xml:space="preserve">Viscosidad newtoniana. El tensor de viscosidad para fluidos newtonianos.</t>
+    <t xml:space="preserve">Las ecuaciones de Navier-Stokes. </t>
   </si>
   <si>
     <t xml:space="preserve">J4</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Las ecuaciones de Navier-Stokes. </t>
-    </r>
+    <t xml:space="preserve">Flujo vivo y flujo viscoso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M9</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -333,7 +316,7 @@
         <family val="1"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Flujo vivo y flujo viscoso. </t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -346,7 +329,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">V5</t>
+    <t xml:space="preserve">V12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M16</t>
   </si>
   <si>
     <t xml:space="preserve">Tercer parcial</t>
@@ -359,7 +345,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -414,6 +400,16 @@
       <family val="1"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -481,7 +477,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -546,10 +542,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -564,6 +556,18 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="justify" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="justify" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -643,11 +647,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD56"/>
+  <dimension ref="A1:XFD1048576"/>
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="117.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="135.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="10.25"/>
@@ -868,93 +872,93 @@
       <c r="A26" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="16" t="s">
-        <v>38</v>
+      <c r="B26" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="XFC26" s="9"/>
       <c r="XFD26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="XFC27" s="9"/>
       <c r="XFD27" s="9"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="XFC28" s="9"/>
       <c r="XFD28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B29" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="17"/>
+      <c r="B29" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="16"/>
       <c r="XFC29" s="9"/>
       <c r="XFD29" s="9"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C30" s="17"/>
+        <v>48</v>
+      </c>
+      <c r="C30" s="16"/>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B31" s="2" t="s">
         <v>49</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>50</v>
       </c>
       <c r="XFC31" s="9"/>
       <c r="XFD31" s="9"/>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33" s="18" t="s">
         <v>53</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C34" s="19"/>
+        <v>56</v>
+      </c>
+      <c r="C34" s="18"/>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -983,7 +987,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>63</v>
       </c>
@@ -995,93 +999,89 @@
       <c r="A41" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>66</v>
+      <c r="B41" s="17" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B42" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B42" s="4" t="s">
+    </row>
+    <row r="43" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
+      <c r="B43" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B43" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C43" s="17"/>
+      <c r="C43" s="16"/>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B44" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C44" s="17"/>
+      <c r="C44" s="16"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B45" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="B45" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="XFC45" s="9"/>
-      <c r="XFD45" s="9"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B46" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="B46" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="XFC46" s="9"/>
-      <c r="XFD46" s="9"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B47" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B48" s="20" t="s">
         <v>79</v>
-      </c>
-      <c r="B48" s="20" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B49" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="B49" s="20" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50" s="6" t="s">
         <v>83</v>
-      </c>
-      <c r="B50" s="18" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="2" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       <c r="A52" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="21" t="s">
         <v>87</v>
       </c>
     </row>
@@ -1097,27 +1097,38 @@
       <c r="A53" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B53" s="18" t="s">
+      <c r="B53" s="17" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="12" t="s">
+    <row r="54" s="9" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="22" t="s">
         <v>89</v>
       </c>
+      <c r="B54" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="XFC54" s="0"/>
+      <c r="XFD54" s="0"/>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="9"/>
-      <c r="B55" s="9"/>
+      <c r="A55" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B55" s="17" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="9"/>
-      <c r="B56" s="9"/>
-      <c r="D56" s="13"/>
-    </row>
+      <c r="A56" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
